--- a/data/trans_dic/Predimed_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,24; 83,34</t>
+          <t>76,4; 83,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,19; 81,63</t>
+          <t>74,91; 81,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,7; 81,86</t>
+          <t>76,75; 81,67</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,54; 86,1</t>
+          <t>78,82; 86,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,76; 80,19</t>
+          <t>73,18; 80,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,46; 82,62</t>
+          <t>77,08; 82,41</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,67; 95,37</t>
+          <t>77,77; 95,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,57; 79,62</t>
+          <t>67,42; 79,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,85; 92,94</t>
+          <t>76,75; 93,61</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,95; 82,94</t>
+          <t>77,67; 83,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,43; 92,2</t>
+          <t>78,44; 91,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,48; 88,74</t>
+          <t>79,49; 87,9</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>85,06; 91,58</t>
+          <t>85,22; 91,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,52; 85,36</t>
+          <t>68,43; 85,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,65; 86,51</t>
+          <t>75,83; 86,7</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,33; 96,67</t>
+          <t>84,2; 96,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,49; 89,92</t>
+          <t>85,63; 90,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,5; 90,85</t>
+          <t>86,64; 90,82</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,12; 88,02</t>
+          <t>81,97; 87,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,14; 84,88</t>
+          <t>79,42; 85,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,16; 85,26</t>
+          <t>81,24; 85,35</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>368726; 403087</t>
+          <t>369494; 404759</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>325655; 353563</t>
+          <t>324474; 354120</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>703171; 750468</t>
+          <t>703621; 748776</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>336283; 368646</t>
+          <t>337478; 368681</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>269969; 297547</t>
+          <t>271521; 298145</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>619020; 660308</t>
+          <t>615980; 658587</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>499582; 613461</t>
+          <t>500233; 613277</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>108109; 125535</t>
+          <t>106300; 125451</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>615452; 744311</t>
+          <t>614657; 749707</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>744614; 792298</t>
+          <t>741962; 797447</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>736115; 865435</t>
+          <t>736236; 861801</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1505262; 1680576</t>
+          <t>1505517; 1664756</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>372934; 401522</t>
+          <t>373606; 401761</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>544650; 678525</t>
+          <t>543904; 677029</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>932938; 1066869</t>
+          <t>935226; 1069235</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>165699; 192243</t>
+          <t>167432; 192198</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>593164; 623869</t>
+          <t>594084; 624861</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>772122; 810989</t>
+          <t>773374; 810707</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2584898; 2770497</t>
+          <t>2579933; 2764065</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2682050; 2876843</t>
+          <t>2691579; 2894058</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5305186; 5573197</t>
+          <t>5310621; 5579046</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,4; 83,69</t>
+          <t>75,41; 83,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,91; 81,76</t>
+          <t>75,15; 81,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,75; 81,67</t>
+          <t>76,5; 81,67</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,82; 86,11</t>
+          <t>77,95; 85,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,18; 80,35</t>
+          <t>72,65; 79,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,08; 82,41</t>
+          <t>76,71; 81,94</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,77; 95,34</t>
+          <t>74,01; 81,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,42; 79,57</t>
+          <t>69,72; 80,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,75; 93,61</t>
+          <t>74,09; 80,61</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,67; 83,48</t>
+          <t>77,47; 82,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,44; 91,82</t>
+          <t>77,01; 81,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,49; 87,9</t>
+          <t>77,92; 81,82</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>85,22; 91,64</t>
+          <t>86,34; 92,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,43; 85,18</t>
+          <t>79,95; 84,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,83; 86,7</t>
+          <t>83,71; 87,27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84,2; 96,65</t>
+          <t>84,79; 96,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,63; 90,06</t>
+          <t>85,89; 89,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,64; 90,82</t>
+          <t>86,71; 90,81</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>81,97; 87,81</t>
+          <t>81,03; 83,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,42; 85,39</t>
+          <t>80,2; 82,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,24; 85,35</t>
+          <t>81,02; 82,86</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>386981</t>
+          <t>417705</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>340471</t>
+          <t>372700</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>727452</t>
+          <t>790405</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>369494; 404759</t>
+          <t>396761; 438110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>324474; 354120</t>
+          <t>355615; 386807</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>703621; 748776</t>
+          <t>764512; 816150</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>354648</t>
+          <t>376024</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>284726</t>
+          <t>312966</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>639373</t>
+          <t>688991</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>337478; 368681</t>
+          <t>356592; 391537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>271521; 298145</t>
+          <t>297681; 326535</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>615980; 658587</t>
+          <t>665233; 710554</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>560096</t>
+          <t>348077</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>133311</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>677647</t>
+          <t>481389</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>500233; 613277</t>
+          <t>329219; 363804</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>106300; 125451</t>
+          <t>123011; 142466</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>614657; 749707</t>
+          <t>460325; 500781</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>771711</t>
+          <t>840040</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>787363</t>
+          <t>650120</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1559075</t>
+          <t>1490159</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>741962; 797447</t>
+          <t>810329; 867138</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>736236; 861801</t>
+          <t>630353; 668882</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1505517; 1664756</t>
+          <t>1452853; 1525474</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>388742</t>
+          <t>465808</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>636410</t>
+          <t>642501</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1025152</t>
+          <t>1108309</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>373606; 401761</t>
+          <t>448674; 479633</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>543904; 677029</t>
+          <t>621714; 658406</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>935226; 1069235</t>
+          <t>1085929; 1132042</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>183285</t>
+          <t>184258</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>610257</t>
+          <t>678091</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>793542</t>
+          <t>862350</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>167432; 192198</t>
+          <t>168211; 191842</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>594084; 624861</t>
+          <t>662098; 693578</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>773374; 810707</t>
+          <t>840398; 880149</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2645464</t>
+          <t>2631913</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2776776</t>
+          <t>2789690</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5422240</t>
+          <t>5421602</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2579933; 2764065</t>
+          <t>2586771; 2678365</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2691579; 2894058</t>
+          <t>2747836; 2825247</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5310621; 5579046</t>
+          <t>5362731; 5484071</t>
         </is>
       </c>
     </row>
